--- a/growth_mindset_data.xlsx
+++ b/growth_mindset_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Python Projects\Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832F52A6-E726-4BFE-9BE5-AB744C658252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E10E1E3-D2AC-43FF-BF16-643F0E448FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>Quote</t>
   </si>
@@ -60,13 +60,118 @@
   </si>
   <si>
     <t>Make Friends</t>
+  </si>
+  <si>
+    <t>"The only limit to our realization of tomorrow is our doubts of today."</t>
+  </si>
+  <si>
+    <t>Franklin D. Roosevelt</t>
+  </si>
+  <si>
+    <t>"Success is not final, failure is not fatal: It is the courage to continue that counts."</t>
+  </si>
+  <si>
+    <t>Winston Churchill</t>
+  </si>
+  <si>
+    <t>"Whether you think you can or you think you can't, you're right."</t>
+  </si>
+  <si>
+    <t>Henry Ford</t>
+  </si>
+  <si>
+    <t>"The harder you work for something, the greater you'll feel when you achieve it."</t>
+  </si>
+  <si>
+    <t>"Don't watch the clock; do what it does. Keep going."</t>
+  </si>
+  <si>
+    <t>Sam Levenson</t>
+  </si>
+  <si>
+    <t>"Believe you can and you're halfway there."</t>
+  </si>
+  <si>
+    <t>Theodore Roosevelt</t>
+  </si>
+  <si>
+    <t>"It does not matter how slowly you go as long as you do not stop."</t>
+  </si>
+  <si>
+    <t>Confucius</t>
+  </si>
+  <si>
+    <t>"Your attitude, not your aptitude, will determine your altitude."</t>
+  </si>
+  <si>
+    <t>Zig Ziglar</t>
+  </si>
+  <si>
+    <t>"The only way to do great work is to love what you do."</t>
+  </si>
+  <si>
+    <t>Steve Jobs</t>
+  </si>
+  <si>
+    <t>"You don't have to be great to start, but you have to start to be great."</t>
+  </si>
+  <si>
+    <t>"The expert in anything was once a beginner."</t>
+  </si>
+  <si>
+    <t>Helen Hayes</t>
+  </si>
+  <si>
+    <t>"Success is stumbling from failure to failure with no loss of enthusiasm."</t>
+  </si>
+  <si>
+    <t>"Dream big and dare to fail."</t>
+  </si>
+  <si>
+    <t>Norman Vaughan</t>
+  </si>
+  <si>
+    <t>"The only person you are destined to become is the person you decide to be."</t>
+  </si>
+  <si>
+    <t>Ralph Waldo Emerson</t>
+  </si>
+  <si>
+    <t>"Challenges are what make life interesting. Overcoming them is what makes life meaningful."</t>
+  </si>
+  <si>
+    <t>Joshua J. Marine</t>
+  </si>
+  <si>
+    <t>"You are never too old to set another goal or to dream a new dream."</t>
+  </si>
+  <si>
+    <t>C.S. Lewis</t>
+  </si>
+  <si>
+    <t>"The future belongs to those who believe in the beauty of their dreams."</t>
+  </si>
+  <si>
+    <t>Eleanor Roosevelt</t>
+  </si>
+  <si>
+    <t>"Failure is the opportunity to begin again more intelligently."</t>
+  </si>
+  <si>
+    <t>"What you get by achieving your goals is not as important as what you become by achieving your goals."</t>
+  </si>
+  <si>
+    <t>"The mind is everything. What you think, you become."</t>
+  </si>
+  <si>
+    <t>Buddha</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +188,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF404040"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -135,13 +246,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,10 +559,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.28515625" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -474,6 +588,166 @@
       </c>
       <c r="B3" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="69" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="69" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/growth_mindset_data.xlsx
+++ b/growth_mindset_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Python Projects\Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E10E1E3-D2AC-43FF-BF16-643F0E448FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5891555-34E9-4AA6-A87A-3FCEE6589F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,7 +562,7 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
+    <col min="1" max="1" width="51.42578125" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/growth_mindset_data.xlsx
+++ b/growth_mindset_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Python Projects\Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5891555-34E9-4AA6-A87A-3FCEE6589F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A22EE2D-13B3-4764-B505-4C10C9E1FEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,116 +62,116 @@
     <t>Make Friends</t>
   </si>
   <si>
-    <t>"The only limit to our realization of tomorrow is our doubts of today."</t>
-  </si>
-  <si>
     <t>Franklin D. Roosevelt</t>
   </si>
   <si>
-    <t>"Success is not final, failure is not fatal: It is the courage to continue that counts."</t>
-  </si>
-  <si>
     <t>Winston Churchill</t>
   </si>
   <si>
-    <t>"Whether you think you can or you think you can't, you're right."</t>
-  </si>
-  <si>
     <t>Henry Ford</t>
   </si>
   <si>
-    <t>"The harder you work for something, the greater you'll feel when you achieve it."</t>
-  </si>
-  <si>
-    <t>"Don't watch the clock; do what it does. Keep going."</t>
-  </si>
-  <si>
     <t>Sam Levenson</t>
   </si>
   <si>
-    <t>"Believe you can and you're halfway there."</t>
-  </si>
-  <si>
     <t>Theodore Roosevelt</t>
   </si>
   <si>
-    <t>"It does not matter how slowly you go as long as you do not stop."</t>
-  </si>
-  <si>
     <t>Confucius</t>
   </si>
   <si>
-    <t>"Your attitude, not your aptitude, will determine your altitude."</t>
-  </si>
-  <si>
     <t>Zig Ziglar</t>
   </si>
   <si>
-    <t>"The only way to do great work is to love what you do."</t>
-  </si>
-  <si>
     <t>Steve Jobs</t>
   </si>
   <si>
-    <t>"You don't have to be great to start, but you have to start to be great."</t>
-  </si>
-  <si>
-    <t>"The expert in anything was once a beginner."</t>
-  </si>
-  <si>
     <t>Helen Hayes</t>
   </si>
   <si>
-    <t>"Success is stumbling from failure to failure with no loss of enthusiasm."</t>
-  </si>
-  <si>
-    <t>"Dream big and dare to fail."</t>
-  </si>
-  <si>
     <t>Norman Vaughan</t>
   </si>
   <si>
-    <t>"The only person you are destined to become is the person you decide to be."</t>
-  </si>
-  <si>
     <t>Ralph Waldo Emerson</t>
   </si>
   <si>
-    <t>"Challenges are what make life interesting. Overcoming them is what makes life meaningful."</t>
-  </si>
-  <si>
     <t>Joshua J. Marine</t>
   </si>
   <si>
-    <t>"You are never too old to set another goal or to dream a new dream."</t>
-  </si>
-  <si>
     <t>C.S. Lewis</t>
   </si>
   <si>
-    <t>"The future belongs to those who believe in the beauty of their dreams."</t>
-  </si>
-  <si>
     <t>Eleanor Roosevelt</t>
   </si>
   <si>
-    <t>"Failure is the opportunity to begin again more intelligently."</t>
-  </si>
-  <si>
-    <t>"What you get by achieving your goals is not as important as what you become by achieving your goals."</t>
-  </si>
-  <si>
-    <t>"The mind is everything. What you think, you become."</t>
-  </si>
-  <si>
     <t>Buddha</t>
+  </si>
+  <si>
+    <t>The only limit to our realization of tomorrow is our doubts of today.</t>
+  </si>
+  <si>
+    <t>Success is not final, failure is not fatal: It is the courage to continue that counts.</t>
+  </si>
+  <si>
+    <t>Whether you think you can or you think you can't, you're right.</t>
+  </si>
+  <si>
+    <t>The harder you work for something, the greater you'll feel when you achieve it.</t>
+  </si>
+  <si>
+    <t>Don't watch the clock; do what it does. Keep going.</t>
+  </si>
+  <si>
+    <t>Believe you can and you're halfway there.</t>
+  </si>
+  <si>
+    <t>It does not matter how slowly you go as long as you do not stop.</t>
+  </si>
+  <si>
+    <t>Your attitude, not your aptitude, will determine your altitude.</t>
+  </si>
+  <si>
+    <t>The only way to do great work is to love what you do.</t>
+  </si>
+  <si>
+    <t>You don't have to be great to start, but you have to start to be great.</t>
+  </si>
+  <si>
+    <t>The expert in anything was once a beginner.</t>
+  </si>
+  <si>
+    <t>Success is stumbling from failure to failure with no loss of enthusiasm.</t>
+  </si>
+  <si>
+    <t>Dream big and dare to fail.</t>
+  </si>
+  <si>
+    <t>The only person you are destined to become is the person you decide to be.</t>
+  </si>
+  <si>
+    <t>Challenges are what make life interesting. Overcoming them is what makes life meaningful.</t>
+  </si>
+  <si>
+    <t>You are never too old to set another goal or to dream a new dream.</t>
+  </si>
+  <si>
+    <t>The future belongs to those who believe in the beauty of their dreams.</t>
+  </si>
+  <si>
+    <t>Failure is the opportunity to begin again more intelligently.</t>
+  </si>
+  <si>
+    <t>What you get by achieving your goals is not as important as what you become by achieving your goals.</t>
+  </si>
+  <si>
+    <t>The mind is everything. What you think, you become.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,12 +188,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF404040"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -246,16 +240,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,11 +553,11 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.42578125" customWidth="1"/>
+    <col min="1" max="1" width="114.85546875" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -582,7 +573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -590,164 +581,164 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="6" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="9" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="11" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3" t="s">
+    </row>
+    <row r="13" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="15" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="18" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="20" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="3" t="s">
+    </row>
+    <row r="21" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="69" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="69" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/growth_mindset_data.xlsx
+++ b/growth_mindset_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Python Projects\Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A22EE2D-13B3-4764-B505-4C10C9E1FEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AB4F87-EFB8-4729-B673-DD2DBB5F6D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>Quote</t>
   </si>
@@ -29,16 +29,7 @@
     <t>Author</t>
   </si>
   <si>
-    <t>The only limit is your imagination.</t>
-  </si>
-  <si>
     <t>Unknown</t>
-  </si>
-  <si>
-    <t>Embrace challenges and grow.</t>
-  </si>
-  <si>
-    <t>Carol Dweck</t>
   </si>
   <si>
     <t>Goal</t>
@@ -550,11 +541,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="114.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -567,178 +558,162 @@
     </row>
     <row r="2" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -757,15 +732,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>75</v>
@@ -773,7 +748,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>50</v>
@@ -781,7 +756,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>15</v>
@@ -789,7 +764,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -797,7 +772,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>20</v>

--- a/growth_mindset_data.xlsx
+++ b/growth_mindset_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Python Projects\Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AB4F87-EFB8-4729-B673-DD2DBB5F6D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6ED39B9-6E18-4C3B-93F1-5EC84F856AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
